--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-04 21:47)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 10:24)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +216,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 12.95 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 5.70 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 14.46 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 4.92 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -267,7 +267,7 @@
     <t>peak electrical draw checked against 1000 W across the whole mission (Deliverable 6)</t>
   </si>
   <si>
-    <t>MTOM = 4.146 kg vs 6.0 kg limit</t>
+    <t>MTOM = 4.578 kg vs 6.0 kg limit</t>
   </si>
   <si>
     <t>cost tracking -- not a performance-model quantity</t>
@@ -285,13 +285,13 @@
     <t>paint/marking scheme -- not modelled</t>
   </si>
   <si>
-    <t>MTOM = 4.146 kg vs 5.40 kg (90% of 6 kg)</t>
+    <t>MTOM = 4.578 kg vs 5.40 kg (90% of 6 kg)</t>
   </si>
   <si>
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 0.755 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 1.554 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
   </si>
 </sst>
 </file>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 10:24)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 20:19)</t>
   </si>
   <si>
     <t>ID</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 20:19)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 20:28)</t>
   </si>
   <si>
     <t>ID</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ceaa8977d2236823/Documents/GitHub/451-DBF-Team01/Aicraft Performance Simulation/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_514D7E17CE870278CB9AADC4EC012D16118A4293" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{69CFEB0D-693F-470E-8FFE-ED7E68D66822}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Deliverable 9" sheetId="1" r:id="rId2"/>
+    <sheet name="Deliverable 9" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" fullCalcOnLoad="true"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
-  <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 20:28)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="93">
+  <si>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-05 21:45)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +223,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 14.46 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 4.92 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 12.90 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 5.68 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -267,7 +274,7 @@
     <t>peak electrical draw checked against 1000 W across the whole mission (Deliverable 6)</t>
   </si>
   <si>
-    <t>MTOM = 4.578 kg vs 6.0 kg limit</t>
+    <t>MTOM = 4.052 kg vs 6.0 kg limit</t>
   </si>
   <si>
     <t>cost tracking -- not a performance-model quantity</t>
@@ -285,20 +292,20 @@
     <t>paint/marking scheme -- not modelled</t>
   </si>
   <si>
-    <t>MTOM = 4.578 kg vs 5.40 kg (90% of 6 kg)</t>
+    <t>MTOM = 4.052 kg vs 5.40 kg (90% of 6 kg)</t>
   </si>
   <si>
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 1.554 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 2.183 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -312,7 +319,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -320,474 +327,795 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D32"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="56.5546875" customWidth="true"/>
-    <col min="2" max="2" width="35.77734375" customWidth="true"/>
-    <col min="3" max="3" width="6" customWidth="true"/>
-    <col min="4" max="4" width="88.88671875" customWidth="true"/>
+    <col min="1" max="1" width="56.5546875" customWidth="1"/>
+    <col min="2" max="2" width="48.88671875" customWidth="1"/>
+    <col min="3" max="3" width="29.6640625" customWidth="1"/>
+    <col min="4" max="4" width="88.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0"/>
-      <c r="C1" s="0"/>
-      <c r="D1" s="0"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="0" t="s">
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="C7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="C8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="0" t="s">
+      <c r="C9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="0" t="s">
+      <c r="C10" t="s">
+        <v>65</v>
+      </c>
+      <c r="D10" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="C11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="0" t="s">
+      <c r="D12" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="0" t="s">
+      <c r="C13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="0" t="s">
+      <c r="C14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" s="0" t="s">
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" t="s">
         <v>46</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="0" t="s">
+      <c r="D16" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="0" t="s">
+      <c r="C17" t="s">
+        <v>65</v>
+      </c>
+      <c r="D17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D18" s="0" t="s">
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D19" s="0" t="s">
+      <c r="C19" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" t="s">
         <v>50</v>
       </c>
-      <c r="C20" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D20" s="0" t="s">
+      <c r="C20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" t="s">
         <v>51</v>
       </c>
-      <c r="C21" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="0" t="s">
+      <c r="C21" t="s">
+        <v>65</v>
+      </c>
+      <c r="D21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D22" s="0" t="s">
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="0" t="s">
+      <c r="C23" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="0" t="s">
+      <c r="D23" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="0" t="s">
+      <c r="C24" t="s">
         <v>64</v>
       </c>
-      <c r="D24" s="0" t="s">
+      <c r="D24" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="0" t="s">
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" t="s">
         <v>56</v>
       </c>
-      <c r="C26" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D26" s="0" t="s">
+      <c r="C26" t="s">
+        <v>65</v>
+      </c>
+      <c r="D26" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" t="s">
         <v>57</v>
       </c>
-      <c r="C27" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27" s="0" t="s">
+      <c r="C27" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" t="s">
         <v>58</v>
       </c>
-      <c r="C28" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="0" t="s">
+      <c r="C28" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="0" t="s">
+      <c r="C29" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>29</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="0" t="s">
+      <c r="C30" t="s">
         <v>64</v>
       </c>
-      <c r="D30" s="0" t="s">
+      <c r="D30" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="0" t="s">
+      <c r="C31" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" t="s">
         <v>62</v>
       </c>
-      <c r="C32" s="0" t="s">
+      <c r="C32" t="s">
         <v>64</v>
       </c>
-      <c r="D32" s="0" t="s">
+      <c r="D32" t="s">
         <v>92</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 09:34)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 10:59)</t>
   </si>
   <si>
     <t>ID</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -6,8 +6,9 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Deliverable 9" sheetId="1" r:id="rId2"/>
+    <sheet name="Deliverable 9" sheetId="2" r:id="rId3"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
@@ -15,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 09:34)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 13:56)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +217,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 12.90 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 5.68 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 12.88 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 5.67 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -291,7 +292,7 @@
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 2.183 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 2.186 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
   </si>
 </sst>
 </file>
@@ -335,15 +336,15 @@
 </styleSheet>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="56.5546875" customWidth="true"/>
-    <col min="2" max="2" width="35.77734375" customWidth="true"/>
-    <col min="3" max="3" width="6" customWidth="true"/>
-    <col min="4" max="4" width="88.88671875" customWidth="true"/>
+    <col min="1" max="1" width="61.140625" customWidth="true"/>
+    <col min="2" max="2" width="39.28515625" customWidth="true"/>
+    <col min="3" max="3" width="6.5703125" customWidth="true"/>
+    <col min="4" max="4" width="97.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -13,9 +13,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="125" uniqueCount="93">
-  <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 10:59)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
+  <si>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:12)</t>
   </si>
   <si>
     <t>ID</t>
@@ -207,19 +207,19 @@
     <t>Status</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>N/A</t>
+    <t>Verified</t>
+  </si>
+  <si>
+    <t>Open</t>
   </si>
   <si>
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 12.90 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 5.68 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 13.44 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 7.54 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -291,7 +291,73 @@
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 2.183 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 1.917 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Flight test: fly the as-built aircraft through a representative lap configuration at the payload condition, verify handling and recovery; before competition.</t>
+  </si>
+  <si>
+    <t>Flight test: land the as-built aircraft on the actual grass/dirt surface, inspect the airframe for damage after each landing; during flight-test sessions.</t>
+  </si>
+  <si>
+    <t>Inspection + flight test: review the structure for exposed hazards (prop, sharp edges) and confirm nothing separates on a hard landing; before first flight.</t>
+  </si>
+  <si>
+    <t>Physical inspection: verify connector type, polarity, and secure mounting once the battery and fuselage are both built; at integration.</t>
+  </si>
+  <si>
+    <t>Physical measurement: measure as-built prop-to-ground and prop-to-fuselage clearance once the airframe and gear are assembled; at integration.</t>
+  </si>
+  <si>
+    <t>Physical fit-check: fold/disassemble the as-built aircraft and measure the stowed envelope against 75x75x150 cm; once assembly is complete.</t>
+  </si>
+  <si>
+    <t>Timed demonstration: time a team member performing the configuration change on the as-built aircraft; during a practice/readiness review.</t>
+  </si>
+  <si>
+    <t>Timed demonstration: time battery and payload installation on the as-built aircraft; during a practice/readiness review.</t>
+  </si>
+  <si>
+    <t>Physical demonstration: remove and install the battery by hand, confirm no tools are needed; at integration.</t>
+  </si>
+  <si>
+    <t>Physical inspection: verify mounting hardware secures both under expected flight loads; at integration.</t>
+  </si>
+  <si>
+    <t>Physical inspection: confirm no aircraft modification is needed to swap battery or payload; at integration.</t>
+  </si>
+  <si>
+    <t>Flight test: fly with payload installed, assess handling qualities qualitatively; during flight-test sessions.</t>
+  </si>
+  <si>
+    <t>Flight test: fly without payload, assess handling qualities qualitatively; during flight-test sessions.</t>
+  </si>
+  <si>
+    <t>Flight test: have a non-team-member pilot fly the aircraft and report on handling; during a flight-test session.</t>
+  </si>
+  <si>
+    <t>Bench/ground test: verify the telemetry/avionics package powers on and logs or transmits data correctly; at avionics integration.</t>
+  </si>
+  <si>
+    <t>Cost audit: tally as-built/as-purchased costs against the $400 cap; ongoing, finalized before competition.</t>
+  </si>
+  <si>
+    <t>Program review: confirm the aircraft is flight-ready against the team's build schedule; at the Week 12 milestone.</t>
+  </si>
+  <si>
+    <t>Documentation review: compile and review as-built design-change justifications; before final report submission.</t>
+  </si>
+  <si>
+    <t>Flight test: fly 3 consecutive take-off/landing cycles without repair, inspect the airframe between flights; during flight-test sessions.</t>
+  </si>
+  <si>
+    <t>Visual demonstration: view the as-built, as-painted aircraft from 200 m and confirm visibility; during a flight-test or ground check.</t>
+  </si>
+  <si>
+    <t>Timed demonstration: simulate a representative field repair on the as-built aircraft and time it; during a practice/readiness review.</t>
   </si>
 </sst>
 </file>
@@ -337,13 +403,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="56.5546875" customWidth="true"/>
     <col min="2" max="2" width="35.77734375" customWidth="true"/>
-    <col min="3" max="3" width="6" customWidth="true"/>
+    <col min="3" max="3" width="7.33203125" customWidth="true"/>
     <col min="4" max="4" width="88.88671875" customWidth="true"/>
+    <col min="5" max="5" width="123.77734375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -353,6 +420,7 @@
       <c r="B1" s="0"/>
       <c r="C1" s="0"/>
       <c r="D1" s="0"/>
+      <c r="E1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
@@ -367,6 +435,9 @@
       <c r="D2" s="0" t="s">
         <v>66</v>
       </c>
+      <c r="E2" s="0" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
@@ -381,6 +452,7 @@
       <c r="D3" s="0" t="s">
         <v>67</v>
       </c>
+      <c r="E3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
@@ -395,6 +467,7 @@
       <c r="D4" s="0" t="s">
         <v>68</v>
       </c>
+      <c r="E4" s="0"/>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
@@ -409,6 +482,7 @@
       <c r="D5" s="0" t="s">
         <v>69</v>
       </c>
+      <c r="E5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
@@ -423,6 +497,9 @@
       <c r="D6" s="0" t="s">
         <v>70</v>
       </c>
+      <c r="E6" s="0" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
@@ -437,6 +514,9 @@
       <c r="D7" s="0" t="s">
         <v>71</v>
       </c>
+      <c r="E7" s="0" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
@@ -451,6 +531,9 @@
       <c r="D8" s="0" t="s">
         <v>72</v>
       </c>
+      <c r="E8" s="0" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
@@ -465,6 +548,9 @@
       <c r="D9" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="E9" s="0" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
@@ -479,6 +565,9 @@
       <c r="D10" s="0" t="s">
         <v>73</v>
       </c>
+      <c r="E10" s="0" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
@@ -493,6 +582,9 @@
       <c r="D11" s="0" t="s">
         <v>74</v>
       </c>
+      <c r="E11" s="0" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -507,6 +599,7 @@
       <c r="D12" s="0" t="s">
         <v>75</v>
       </c>
+      <c r="E12" s="0"/>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
@@ -521,6 +614,9 @@
       <c r="D13" s="0" t="s">
         <v>76</v>
       </c>
+      <c r="E13" s="0" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
@@ -535,6 +631,9 @@
       <c r="D14" s="0" t="s">
         <v>76</v>
       </c>
+      <c r="E14" s="0" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
@@ -549,6 +648,9 @@
       <c r="D15" s="0" t="s">
         <v>77</v>
       </c>
+      <c r="E15" s="0" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="0" t="s">
@@ -563,6 +665,7 @@
       <c r="D16" s="0" t="s">
         <v>78</v>
       </c>
+      <c r="E16" s="0"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
@@ -577,6 +680,9 @@
       <c r="D17" s="0" t="s">
         <v>77</v>
       </c>
+      <c r="E17" s="0" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
@@ -591,6 +697,9 @@
       <c r="D18" s="0" t="s">
         <v>77</v>
       </c>
+      <c r="E18" s="0" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="0" t="s">
@@ -605,6 +714,9 @@
       <c r="D19" s="0" t="s">
         <v>79</v>
       </c>
+      <c r="E19" s="0" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
@@ -619,6 +731,9 @@
       <c r="D20" s="0" t="s">
         <v>80</v>
       </c>
+      <c r="E20" s="0" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
@@ -633,6 +748,9 @@
       <c r="D21" s="0" t="s">
         <v>81</v>
       </c>
+      <c r="E21" s="0" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="0" t="s">
@@ -647,6 +765,9 @@
       <c r="D22" s="0" t="s">
         <v>82</v>
       </c>
+      <c r="E22" s="0" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
@@ -661,6 +782,7 @@
       <c r="D23" s="0" t="s">
         <v>83</v>
       </c>
+      <c r="E23" s="0"/>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
@@ -675,6 +797,7 @@
       <c r="D24" s="0" t="s">
         <v>84</v>
       </c>
+      <c r="E24" s="0"/>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
@@ -689,6 +812,9 @@
       <c r="D25" s="0" t="s">
         <v>85</v>
       </c>
+      <c r="E25" s="0" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="0" t="s">
@@ -703,6 +829,9 @@
       <c r="D26" s="0" t="s">
         <v>86</v>
       </c>
+      <c r="E26" s="0" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="0" t="s">
@@ -717,6 +846,9 @@
       <c r="D27" s="0" t="s">
         <v>87</v>
       </c>
+      <c r="E27" s="0" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="0" t="s">
@@ -731,6 +863,9 @@
       <c r="D28" s="0" t="s">
         <v>88</v>
       </c>
+      <c r="E28" s="0" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="0" t="s">
@@ -745,6 +880,9 @@
       <c r="D29" s="0" t="s">
         <v>89</v>
       </c>
+      <c r="E29" s="0" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="0" t="s">
@@ -759,6 +897,7 @@
       <c r="D30" s="0" t="s">
         <v>90</v>
       </c>
+      <c r="E30" s="0"/>
     </row>
     <row r="31">
       <c r="A31" s="0" t="s">
@@ -773,6 +912,9 @@
       <c r="D31" s="0" t="s">
         <v>91</v>
       </c>
+      <c r="E31" s="0" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="0" t="s">
@@ -787,6 +929,7 @@
       <c r="D32" s="0" t="s">
         <v>92</v>
       </c>
+      <c r="E32" s="0"/>
     </row>
   </sheetData>
 </worksheet>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:12)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:17)</t>
   </si>
   <si>
     <t>ID</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:17)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:29)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +216,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 13.44 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 7.54 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 11.11 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 7.45 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -291,7 +291,7 @@
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 1.917 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 2.468 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
   </si>
   <si>
     <t>Action</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:29)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 09:01)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +216,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 11.11 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 7.45 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 9.15 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 9.11 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -267,7 +267,7 @@
     <t>peak electrical draw checked against 1000 W across the whole mission (Deliverable 6)</t>
   </si>
   <si>
-    <t>MTOM = 4.052 kg vs 6.0 kg limit</t>
+    <t>MTOM = 3.391 kg vs 6.0 kg limit</t>
   </si>
   <si>
     <t>cost tracking -- not a performance-model quantity</t>
@@ -285,13 +285,13 @@
     <t>paint/marking scheme -- not modelled</t>
   </si>
   <si>
-    <t>MTOM = 4.052 kg vs 5.40 kg (90% of 6 kg)</t>
+    <t>MTOM = 3.391 kg vs 5.40 kg (90% of 6 kg)</t>
   </si>
   <si>
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 2.468 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 2.428 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
   </si>
   <si>
     <t>Action</t>
@@ -406,11 +406,11 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="56.5546875" customWidth="true"/>
-    <col min="2" max="2" width="35.77734375" customWidth="true"/>
-    <col min="3" max="3" width="7.33203125" customWidth="true"/>
-    <col min="4" max="4" width="88.88671875" customWidth="true"/>
-    <col min="5" max="5" width="123.77734375" customWidth="true"/>
+    <col min="1" max="1" width="61.140625" customWidth="true"/>
+    <col min="2" max="2" width="39.28515625" customWidth="true"/>
+    <col min="3" max="3" width="8.42578125" customWidth="true"/>
+    <col min="4" max="4" width="97.7109375" customWidth="true"/>
+    <col min="5" max="5" width="135.28515625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 09:01)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 11:11)</t>
   </si>
   <si>
     <t>ID</t>
@@ -406,11 +406,11 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="61.140625" customWidth="true"/>
-    <col min="2" max="2" width="39.28515625" customWidth="true"/>
-    <col min="3" max="3" width="8.42578125" customWidth="true"/>
-    <col min="4" max="4" width="97.7109375" customWidth="true"/>
-    <col min="5" max="5" width="135.28515625" customWidth="true"/>
+    <col min="1" max="1" width="56.5546875" customWidth="true"/>
+    <col min="2" max="2" width="35.77734375" customWidth="true"/>
+    <col min="3" max="3" width="7.33203125" customWidth="true"/>
+    <col min="4" max="4" width="88.88671875" customWidth="true"/>
+    <col min="5" max="5" width="123.77734375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 11:11)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 11:55)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +216,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 9.15 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 9.11 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 9.14 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 8.95 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 11:55)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 15:03)</t>
   </si>
   <si>
     <t>ID</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 15:03)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-06 17:29)</t>
   </si>
   <si>
     <t>ID</t>
@@ -216,10 +216,10 @@
     <t>Detail</t>
   </si>
   <si>
-    <t>computed 9.14 m vs limit 25.0 m (Deliverable 2)</t>
-  </si>
-  <si>
-    <t>ROC_max = 8.95 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
+    <t>computed 11.11 m vs limit 25.0 m (Deliverable 2)</t>
+  </si>
+  <si>
+    <t>ROC_max = 7.45 m/s &gt; 0, so the modelled climb reaches 30 m (Deliverable 3)</t>
   </si>
   <si>
     <t>Deliverable 6 simulates exactly 3 laps (R3-cited) and checks the energy budget covers them</t>
@@ -267,7 +267,7 @@
     <t>peak electrical draw checked against 1000 W across the whole mission (Deliverable 6)</t>
   </si>
   <si>
-    <t>MTOM = 3.391 kg vs 6.0 kg limit</t>
+    <t>MTOM = 4.052 kg vs 6.0 kg limit</t>
   </si>
   <si>
     <t>cost tracking -- not a performance-model quantity</t>
@@ -285,13 +285,13 @@
     <t>paint/marking scheme -- not modelled</t>
   </si>
   <si>
-    <t>MTOM = 3.391 kg vs 5.40 kg (90% of 6 kg)</t>
+    <t>MTOM = 4.052 kg vs 5.40 kg (90% of 6 kg)</t>
   </si>
   <si>
     <t>mechanical design / assembly process -- not modelled</t>
   </si>
   <si>
-    <t>Deliverable 8 found a maximum payload of 2.428 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
+    <t>Deliverable 8 found a maximum payload of 2.468 kg while holding every other constraint, vs. the 0.52 kg R14 requires</t>
   </si>
   <si>
     <t>Action</t>

--- a/Aicraft Performance Simulation/RequirementsValidation.xlsx
+++ b/Aicraft Performance Simulation/RequirementsValidation.xlsx
@@ -15,7 +15,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="147" uniqueCount="115">
   <si>
-    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 15:03)</t>
+    <t>Deliverable 9 -- Requirements Validation (last run: 2026-10-07 15:05)</t>
   </si>
   <si>
     <t>ID</t>
